--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -77,7 +77,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -283,7 +283,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -489,7 +489,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -695,7 +695,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -901,7 +901,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -3711,19 +3711,19 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Date Worked 1 (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
   </si>
   <si>
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected.</t>
   </si>
   <si>
-    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
-  </si>
-  <si>
-    <t>Processed Date and Date Worked 1</t>
-  </si>
-  <si>
-    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Date Worked 1 starts empty.</t>
+    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
+  </si>
+  <si>
+    <t>Processed Date and Latest Date Worked</t>
+  </si>
+  <si>
+    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Latest Date Worked starts empty.</t>
   </si>
   <si>
     <t>Processed Date is filled in wherever the row had something to fill it with: the date written into the Notes where there was one, otherwise the Insurance Check Date. A date from the Notes is never overwritten by a check date. Where the row has neither, it is blank for you to fill in.</t>

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="955">
   <si>
     <t>Claim Status</t>
   </si>
@@ -3913,6 +3913,36 @@
   </si>
   <si>
     <t xml:space="preserve">22853 x1; 22612 x1; 22840 x1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start chat on UHC portal to check the rendering provider status </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for account to get activated again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still processing - check again on 09/16/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for bcbs alabama portal access - Jess sent MR throught fax </t>
+  </si>
+  <si>
+    <t xml:space="preserve">call ins and check provider status on dos - DND rendering provider OON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call ins to get bar code letter if needed and insights on denials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -5988,10 +6018,10 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>115</v>
+        <v>946</v>
       </c>
       <c r="C6" s="3">
         <v>46240</v>
@@ -8383,9 +8413,11 @@
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>945</v>
+      </c>
       <c r="B29" s="13" t="s">
-        <v>302</v>
+        <v>947</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="4">
@@ -9077,7 +9109,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A35" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9725,10 +9757,10 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>127</v>
+        <v>945</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>358</v>
+        <v>948</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4">
@@ -10059,10 +10091,10 @@
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>371</v>
+        <v>949</v>
       </c>
       <c r="C9" s="3">
         <v>46204</v>
@@ -10289,10 +10321,10 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>381</v>
+        <v>950</v>
       </c>
       <c r="C11" s="3">
         <v>46225</v>
@@ -10869,10 +10901,10 @@
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>893</v>
+        <v>951</v>
       </c>
       <c r="C16" s="3">
         <v>46204</v>
@@ -11327,10 +11359,10 @@
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>896</v>
+        <v>952</v>
       </c>
       <c r="C20" s="3">
         <v>46211</v>
@@ -13920,9 +13952,11 @@
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>945</v>
+      </c>
       <c r="B43" s="13" t="s">
-        <v>302</v>
+        <v>947</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="4">
@@ -14014,9 +14048,11 @@
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>945</v>
+      </c>
       <c r="B44" s="13" t="s">
-        <v>302</v>
+        <v>947</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="4">
@@ -14177,7 +14213,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A44" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16329,7 +16365,7 @@
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A17" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16975,10 +17011,10 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>666</v>
+        <v>953</v>
       </c>
       <c r="C6" s="3">
         <v>46197</v>
@@ -17215,10 +17251,10 @@
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>945</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>666</v>
+        <v>953</v>
       </c>
       <c r="C8" s="3">
         <v>46197</v>
@@ -19236,9 +19272,11 @@
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>945</v>
+      </c>
       <c r="B26" s="13" t="s">
-        <v>302</v>
+        <v>947</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="4">
@@ -19491,7 +19529,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A10 A11:A25" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21599,7 +21637,7 @@
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21712,7 +21750,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>878</v>
+        <v>954</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4594" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="955">
   <si>
     <t>Claim Status</t>
   </si>
@@ -6379,8 +6379,8 @@
         <v>2</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>320</v>
+        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
+        <v>2</v>
       </c>
       <c r="N9" s="11">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
@@ -6396,10 +6396,10 @@
         <v>137</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>51</v>
@@ -8620,21 +8620,39 @@
       <c r="K31" s="3">
         <v>46277</v>
       </c>
-      <c r="L31" s="11" t="str">
+      <c r="L31" s="11">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
+        <v>-3</v>
+      </c>
+      <c r="M31" s="11" t="str">
+        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
         <v/>
       </c>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="5"/>
+      <c r="N31" s="11" t="str">
+        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O31" s="6">
+        <v>46280</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="Q31" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S31" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U31" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
@@ -10126,8 +10144,8 @@
         <v>-8</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
+        <v>-8</v>
       </c>
       <c r="N9" s="11">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
@@ -10143,10 +10161,10 @@
         <v>137</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>51</v>
@@ -10474,8 +10492,8 @@
         <v>-2</v>
       </c>
       <c r="M12" s="11">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
+        <v>-2</v>
       </c>
       <c r="N12" s="11">
         <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
@@ -10491,10 +10509,10 @@
         <v>137</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>51</v>
@@ -11052,8 +11070,8 @@
         <v>2</v>
       </c>
       <c r="M17" s="11">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>292</v>
+        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
+        <v>2</v>
       </c>
       <c r="N17" s="11">
         <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
@@ -11069,10 +11087,10 @@
         <v>137</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>51</v>
@@ -11512,8 +11530,8 @@
         <v>5</v>
       </c>
       <c r="M21" s="11">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>325</v>
+        <f ca="1">IF($F21="","",$F21+90-TODAY())</f>
+        <v>5</v>
       </c>
       <c r="N21" s="11">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
@@ -11529,10 +11547,10 @@
         <v>137</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>51</v>
@@ -11860,8 +11878,8 @@
         <v>9</v>
       </c>
       <c r="M24" s="11">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>292</v>
+        <f ca="1">IF($F24="","",$F24+90-TODAY())</f>
+        <v>9</v>
       </c>
       <c r="N24" s="11">
         <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
@@ -11877,10 +11895,10 @@
         <v>137</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T24" s="5" t="s">
         <v>51</v>
@@ -14428,8 +14446,8 @@
         <v>-19</v>
       </c>
       <c r="M2" s="11">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <v>-19</v>
       </c>
       <c r="N2" s="11">
         <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
@@ -14445,10 +14463,10 @@
         <v>137</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>51</v>
@@ -15166,8 +15184,8 @@
         <v>2</v>
       </c>
       <c r="N8" s="11">
-        <f ca="1">IF($C8="","",$C8+60-TODAY())</f>
-        <v>17</v>
+        <f ca="1">IF($C8="","",$C8+540-TODAY())</f>
+        <v>497</v>
       </c>
       <c r="O8" s="6">
         <v>46285</v>
@@ -15185,7 +15203,7 @@
         <v>189</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>205</v>
+        <v>923</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>50</v>
@@ -15286,8 +15304,8 @@
         <v>9</v>
       </c>
       <c r="N9" s="11">
-        <f ca="1">IF($C9="","",$C9+60-TODAY())</f>
-        <v>39</v>
+        <f ca="1">IF($C9="","",$C9+540-TODAY())</f>
+        <v>519</v>
       </c>
       <c r="O9" s="6">
         <v>46292</v>
@@ -15305,7 +15323,7 @@
         <v>189</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>205</v>
+        <v>923</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>50</v>
@@ -17046,8 +17064,8 @@
         <v>-12</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>279</v>
+        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <v>-12</v>
       </c>
       <c r="N6" s="11">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
@@ -17063,10 +17081,10 @@
         <v>137</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>51</v>
@@ -17170,8 +17188,8 @@
         <v>-12</v>
       </c>
       <c r="N7" s="11">
-        <f ca="1">IF($C7="","",$C7+60-TODAY())</f>
-        <v>13</v>
+        <f ca="1">IF($C7="","",$C7+540-TODAY())</f>
+        <v>493</v>
       </c>
       <c r="O7" s="6">
         <v>46271</v>
@@ -17189,7 +17207,7 @@
         <v>189</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>205</v>
+        <v>923</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>50</v>
@@ -17286,8 +17304,8 @@
         <v>-9</v>
       </c>
       <c r="M8" s="11">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>279</v>
+        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
+        <v>-9</v>
       </c>
       <c r="N8" s="11">
         <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
@@ -17303,10 +17321,10 @@
         <v>137</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>51</v>
@@ -17402,8 +17420,8 @@
         <v>-9</v>
       </c>
       <c r="M9" s="11">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>278</v>
+        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
+        <v>-9</v>
       </c>
       <c r="N9" s="11">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
@@ -17419,10 +17437,10 @@
         <v>137</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>51</v>
@@ -20200,8 +20218,8 @@
         <v>-10</v>
       </c>
       <c r="M6" s="11">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <v>-10</v>
       </c>
       <c r="N6" s="11">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
@@ -20217,10 +20235,10 @@
         <v>137</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>51</v>
@@ -21406,21 +21424,39 @@
       <c r="K17" s="3">
         <v>46273</v>
       </c>
-      <c r="L17" s="11" t="str">
+      <c r="L17" s="11">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v>-11</v>
+      </c>
+      <c r="M17" s="11" t="str">
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
         <v/>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="5"/>
+      <c r="N17" s="11" t="str">
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O17" s="6">
+        <v>46272</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="Q17" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U17" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -235,20 +235,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -438,20 +424,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -647,20 +619,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -853,20 +811,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1056,20 +1000,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -5407,7 +5337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5444,10 +5374,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5568,11 +5497,8 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="13"/>
       <c r="C2" s="3">
@@ -5680,9 +5606,8 @@
       <c r="AN2" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO2" s="5"/>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="13"/>
       <c r="C3" s="3">
@@ -5788,9 +5713,8 @@
       <c r="AN3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="5"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>78</v>
       </c>
@@ -5898,11 +5822,8 @@
       <c r="AN4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>86</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
@@ -6012,11 +5933,8 @@
       <c r="AN5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>98</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>945</v>
       </c>
@@ -6124,11 +6042,8 @@
       <c r="AN6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>122</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="13"/>
       <c r="C7" s="3"/>
@@ -6228,9 +6143,8 @@
       <c r="AN7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO7" s="5"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>127</v>
       </c>
@@ -6336,11 +6250,8 @@
       <c r="AN8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>134</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -6450,11 +6361,8 @@
       <c r="AN9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>138</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="13"/>
       <c r="C10" s="3"/>
@@ -6554,9 +6462,8 @@
       <c r="AN10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO10" s="5"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="13"/>
       <c r="C11" s="3"/>
@@ -6656,9 +6563,8 @@
       <c r="AN11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO11" s="5"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>127</v>
       </c>
@@ -6764,11 +6670,8 @@
       <c r="AN12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>145</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="13"/>
       <c r="C13" s="3">
@@ -6872,9 +6775,8 @@
       <c r="AN13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO13" s="5"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="13"/>
       <c r="C14" s="3">
@@ -6980,9 +6882,8 @@
       <c r="AN14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO14" s="5"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
@@ -7082,11 +6983,8 @@
       <c r="AN15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>172</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
@@ -7186,11 +7084,8 @@
       <c r="AN16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>196</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="13"/>
       <c r="C17" s="3"/>
@@ -7290,9 +7185,8 @@
       <c r="AN17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO17" s="5"/>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
@@ -7396,11 +7290,8 @@
       <c r="AN18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>212</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="13"/>
       <c r="C19" s="3"/>
@@ -7500,9 +7391,8 @@
       <c r="AN19" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO19" s="5"/>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3">
@@ -7606,11 +7496,8 @@
       <c r="AN20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>234</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3">
@@ -7714,11 +7601,8 @@
       <c r="AN21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>239</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3">
@@ -7822,11 +7706,8 @@
       <c r="AN22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>253</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
@@ -7926,11 +7807,8 @@
       <c r="AN23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>271</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3">
@@ -8034,11 +7912,8 @@
       <c r="AN24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>276</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="13"/>
       <c r="C25" s="3"/>
@@ -8140,9 +8015,8 @@
       <c r="AN25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO25" s="5"/>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
@@ -8232,11 +8106,8 @@
       <c r="AN26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>292</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3">
@@ -8322,11 +8193,8 @@
       <c r="AN27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>295</v>
-      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -8408,11 +8276,8 @@
       <c r="AN28" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO28" s="5" t="s">
-        <v>301</v>
-      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>945</v>
       </c>
@@ -8498,11 +8363,8 @@
       <c r="AN29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO29" s="5" t="s">
-        <v>305</v>
-      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="3"/>
@@ -8584,11 +8446,8 @@
       <c r="AN30" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO30" s="5" t="s">
-        <v>308</v>
-      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>127</v>
       </c>
@@ -8696,11 +8555,8 @@
       <c r="AN31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO31" s="5" t="s">
-        <v>312</v>
-      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
@@ -8791,11 +8647,8 @@
       <c r="AN32" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO32" s="5" t="s">
-        <v>316</v>
-      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="3"/>
@@ -8877,11 +8730,8 @@
       <c r="AN33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO33" s="5" t="s">
-        <v>319</v>
-      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
@@ -8963,11 +8813,8 @@
       <c r="AN34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO34" s="5" t="s">
-        <v>323</v>
-      </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="3"/>
@@ -9051,12 +8898,9 @@
       <c r="AN35" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AO35" s="5" t="s">
-        <v>328</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO35" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN35" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L35">
     <cfRule type="expression" dxfId="99" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -9137,7 +8981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO44"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9175,10 +9019,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -9299,11 +9142,8 @@
       <c r="AN1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="12" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>78</v>
       </c>
@@ -9417,11 +9257,8 @@
       <c r="AN2" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>340</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -9533,11 +9370,8 @@
       <c r="AN3" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>345</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -9651,11 +9485,8 @@
       <c r="AN4" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>350</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -9769,11 +9600,8 @@
       <c r="AN5" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>357</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>945</v>
       </c>
@@ -9881,11 +9709,8 @@
       <c r="AN6" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>362</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
@@ -9987,9 +9812,8 @@
       <c r="AN7" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO7" s="5"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
@@ -10103,11 +9927,8 @@
       <c r="AN8" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>370</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>945</v>
       </c>
@@ -10217,11 +10038,8 @@
       <c r="AN9" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>375</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -10333,11 +10151,8 @@
       <c r="AN10" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>380</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>945</v>
       </c>
@@ -10449,11 +10264,8 @@
       <c r="AN11" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>385</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -10563,11 +10375,8 @@
       <c r="AN12" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>388</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>78</v>
       </c>
@@ -10677,11 +10486,8 @@
       <c r="AN13" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>392</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
@@ -10795,11 +10601,8 @@
       <c r="AN14" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>399</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -10913,11 +10716,8 @@
       <c r="AN15" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>406</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>945</v>
       </c>
@@ -11027,11 +10827,8 @@
       <c r="AN16" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>409</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -11143,11 +10940,8 @@
       <c r="AN17" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>413</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
@@ -11257,9 +11051,8 @@
       <c r="AN18" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO18" s="5"/>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>78</v>
       </c>
@@ -11371,11 +11164,8 @@
       <c r="AN19" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>416</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>945</v>
       </c>
@@ -11487,11 +11277,8 @@
       <c r="AN20" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>418</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
@@ -11603,11 +11390,8 @@
       <c r="AN21" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>421</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>78</v>
       </c>
@@ -11721,11 +11505,8 @@
       <c r="AN22" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>431</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>41</v>
       </c>
@@ -11835,11 +11616,8 @@
       <c r="AN23" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>433</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>78</v>
       </c>
@@ -11949,11 +11727,8 @@
       <c r="AN24" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>437</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>901</v>
       </c>
@@ -12061,11 +11836,8 @@
       <c r="AN25" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO25" s="5" t="s">
-        <v>440</v>
-      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>78</v>
       </c>
@@ -12177,11 +11949,8 @@
       <c r="AN26" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>444</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>127</v>
       </c>
@@ -12295,11 +12064,8 @@
       <c r="AN27" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>447</v>
-      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3">
@@ -12405,11 +12171,8 @@
       <c r="AN28" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO28" s="5" t="s">
-        <v>454</v>
-      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="3">
@@ -12521,11 +12284,8 @@
       <c r="AN29" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO29" s="5" t="s">
-        <v>460</v>
-      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="3">
@@ -12633,11 +12393,8 @@
       <c r="AN30" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO30" s="5" t="s">
-        <v>473</v>
-      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="3">
@@ -12745,11 +12502,8 @@
       <c r="AN31" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO31" s="5" t="s">
-        <v>478</v>
-      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>41</v>
       </c>
@@ -12859,11 +12613,8 @@
       <c r="AN32" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO32" s="5" t="s">
-        <v>482</v>
-      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="3"/>
@@ -12965,11 +12716,8 @@
       <c r="AN33" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO33" s="5" t="s">
-        <v>489</v>
-      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
@@ -13071,11 +12819,8 @@
       <c r="AN34" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO34" s="5" t="s">
-        <v>492</v>
-      </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="3">
@@ -13185,9 +12930,8 @@
       <c r="AN35" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO35" s="5"/>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>41</v>
       </c>
@@ -13301,11 +13045,8 @@
       <c r="AN36" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO36" s="5" t="s">
-        <v>502</v>
-      </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="3"/>
@@ -13407,11 +13148,8 @@
       <c r="AN37" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO37" s="5" t="s">
-        <v>504</v>
-      </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3">
@@ -13523,9 +13261,8 @@
       <c r="AN38" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO38" s="5"/>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="3">
@@ -13633,11 +13370,8 @@
       <c r="AN39" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO39" s="5" t="s">
-        <v>509</v>
-      </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="3"/>
@@ -13741,11 +13475,8 @@
       <c r="AN40" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO40" s="5" t="s">
-        <v>512</v>
-      </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
@@ -13855,11 +13586,8 @@
       <c r="AN41" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO41" s="5" t="s">
-        <v>515</v>
-      </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3">
@@ -13965,11 +13693,8 @@
       <c r="AN42" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO42" s="5" t="s">
-        <v>517</v>
-      </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>945</v>
       </c>
@@ -14061,11 +13786,8 @@
       <c r="AN43" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO43" s="5" t="s">
-        <v>526</v>
-      </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>945</v>
       </c>
@@ -14155,12 +13877,9 @@
       <c r="AN44" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="AO44" s="5" t="s">
-        <v>530</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO44" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AN44" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L44">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -14241,7 +13960,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO17"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -14279,10 +13998,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -14403,11 +14121,8 @@
       <c r="AN1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="12" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
@@ -14525,11 +14240,8 @@
       <c r="AN2" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>543</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>78</v>
       </c>
@@ -14647,11 +14359,8 @@
       <c r="AN3" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>549</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>78</v>
       </c>
@@ -14769,11 +14478,8 @@
       <c r="AN4" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>559</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
@@ -14893,11 +14599,8 @@
       <c r="AN5" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>564</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
@@ -15015,11 +14718,8 @@
       <c r="AN6" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>569</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
@@ -15137,11 +14837,8 @@
       <c r="AN7" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>572</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>78</v>
       </c>
@@ -15257,11 +14954,8 @@
       <c r="AN8" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>578</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>78</v>
       </c>
@@ -15379,11 +15073,8 @@
       <c r="AN9" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>587</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>127</v>
       </c>
@@ -15493,11 +15184,8 @@
       <c r="AN10" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>593</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
@@ -15607,11 +15295,8 @@
       <c r="AN11" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>597</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
@@ -15721,11 +15406,8 @@
       <c r="AN12" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>601</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
@@ -15835,11 +15517,8 @@
       <c r="AN13" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>606</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3">
@@ -15951,11 +15630,8 @@
       <c r="AN14" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>617</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3">
@@ -16069,11 +15745,8 @@
       <c r="AN15" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>621</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
@@ -16183,11 +15856,8 @@
       <c r="AN16" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>634</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -16307,12 +15977,9 @@
       <c r="AN17" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>638</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO17" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AN17" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="L2:L17">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -16393,7 +16060,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -16431,10 +16098,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -16555,11 +16221,8 @@
       <c r="AN1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="12" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -16667,11 +16330,8 @@
       <c r="AN2" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>644</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>78</v>
       </c>
@@ -16785,11 +16445,8 @@
       <c r="AN3" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>648</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>78</v>
       </c>
@@ -16905,11 +16562,8 @@
       <c r="AN4" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>653</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>127</v>
       </c>
@@ -17023,11 +16677,8 @@
       <c r="AN5" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>665</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>945</v>
       </c>
@@ -17141,11 +16792,8 @@
       <c r="AN6" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>670</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
@@ -17263,11 +16911,8 @@
       <c r="AN7" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>675</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>945</v>
       </c>
@@ -17377,11 +17022,8 @@
       <c r="AN8" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>678</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -17495,11 +17137,8 @@
       <c r="AN9" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>682</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>78</v>
       </c>
@@ -17609,11 +17248,8 @@
       <c r="AN10" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>685</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>127</v>
       </c>
@@ -17725,11 +17361,8 @@
       <c r="AN11" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>693</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>78</v>
       </c>
@@ -17841,11 +17474,8 @@
       <c r="AN12" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>702</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>901</v>
       </c>
@@ -17959,11 +17589,8 @@
       <c r="AN13" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>708</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>78</v>
       </c>
@@ -18077,11 +17704,8 @@
       <c r="AN14" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>711</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3">
@@ -18187,11 +17811,8 @@
       <c r="AN15" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>715</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
@@ -18293,11 +17914,8 @@
       <c r="AN16" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>717</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -18407,11 +18025,8 @@
       <c r="AN17" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>719</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
@@ -18517,11 +18132,8 @@
       <c r="AN18" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>724</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3">
@@ -18627,11 +18239,8 @@
       <c r="AN19" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>733</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
@@ -18737,11 +18346,8 @@
       <c r="AN20" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>740</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3">
@@ -18845,9 +18451,8 @@
       <c r="AN21" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO21" s="5"/>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3">
@@ -18957,9 +18562,8 @@
       <c r="AN22" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO22" s="5"/>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3">
@@ -19065,11 +18669,8 @@
       <c r="AN23" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>741</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3">
@@ -19175,11 +18776,8 @@
       <c r="AN24" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>752</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3">
@@ -19285,11 +18883,8 @@
       <c r="AN25" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO25" s="5" t="s">
-        <v>757</v>
-      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>945</v>
       </c>
@@ -19381,11 +18976,8 @@
       <c r="AN26" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>763</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
@@ -19471,12 +19063,9 @@
       <c r="AN27" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>774</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO27" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:AN27" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="L2:L27">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -19557,7 +19146,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO18"/>
+  <dimension ref="A1:AN18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -19595,10 +19184,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -19719,11 +19307,8 @@
       <c r="AN1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="12" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>78</v>
       </c>
@@ -19835,11 +19420,8 @@
       <c r="AN2" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>781</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -19947,9 +19529,8 @@
       <c r="AN3" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO3" s="5"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>127</v>
       </c>
@@ -20057,11 +19638,8 @@
       <c r="AN4" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>787</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
@@ -20175,11 +19753,8 @@
       <c r="AN5" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>793</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>78</v>
       </c>
@@ -20289,11 +19864,8 @@
       <c r="AN6" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>798</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -20405,11 +19977,8 @@
       <c r="AN7" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>802</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>127</v>
       </c>
@@ -20515,11 +20084,8 @@
       <c r="AN8" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>806</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -20623,11 +20189,8 @@
       <c r="AN9" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>810</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3">
@@ -20731,11 +20294,8 @@
       <c r="AN10" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>813</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
@@ -20835,11 +20395,8 @@
       <c r="AN11" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>817</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3">
@@ -20945,11 +20502,8 @@
       <c r="AN12" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>828</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3">
@@ -21055,11 +20609,8 @@
       <c r="AN13" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>840</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3">
@@ -21167,11 +20718,8 @@
       <c r="AN14" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>843</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -21287,11 +20835,8 @@
       <c r="AN15" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>853</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3">
@@ -21388,11 +20933,8 @@
       <c r="AN16" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>856</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>127</v>
       </c>
@@ -21500,11 +21042,8 @@
       <c r="AN17" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>860</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
@@ -21597,12 +21136,9 @@
       <c r="AN18" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>861</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO18" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:AN18" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="L2:L18">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="964">
   <si>
     <t>Claim Status</t>
   </si>
@@ -3873,6 +3873,33 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136 claims with a date of service in 2026-06 June, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 - Due in 31+ days: 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4 - Past deadline: 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5 - No limit on file: 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
 </sst>
 </file>
@@ -21238,7 +21265,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>863</v>
+        <v>955</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -21251,37 +21278,37 @@
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>865</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>866</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>867</v>
+        <v>958</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>868</v>
+        <v>959</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>869</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>870</v>
+        <v>961</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>871</v>
+        <v>962</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -21381,7 +21408,7 @@
     </row>
     <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>888</v>
+        <v>963</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -1355,7 +1355,7 @@
     <t>236, 237</t>
   </si>
   <si>
-    <t xml:space="preserve">***Start chat on UHC portal to check the rendering provider status </t>
+    <t xml:space="preserve">Start chat on UHC portal to check the rendering provider status </t>
   </si>
   <si>
     <t>HF559372689</t>
@@ -1916,7 +1916,7 @@
     <t>956, 957</t>
   </si>
   <si>
-    <t>***Waiting for account to get activated again</t>
+    <t>Waiting for account to get activated again</t>
   </si>
   <si>
     <t>HF559371386</t>
@@ -2084,7 +2084,7 @@
     <t>849</t>
   </si>
   <si>
-    <t>***Still processing - check again on 09/16/2026</t>
+    <t>Still processing - check again on 09/16/2026</t>
   </si>
   <si>
     <t>HF547910822</t>
@@ -2123,7 +2123,7 @@
     <t>804</t>
   </si>
   <si>
-    <t xml:space="preserve">***Waiting for bcbs alabama portal access - Jess sent MR throught fax </t>
+    <t xml:space="preserve">Waiting for bcbs alabama portal access - Jess sent MR throught fax </t>
   </si>
   <si>
     <t>HF537490920</t>
@@ -2153,7 +2153,7 @@
     <t>753</t>
   </si>
   <si>
-    <t>***call ins and check provider status on dos - DND rendering provider OON</t>
+    <t>call ins and check provider status on dos - DND rendering provider OON</t>
   </si>
   <si>
     <t>HF499093825</t>
@@ -3008,7 +3008,7 @@
     <t>399, 400, 401, 402</t>
   </si>
   <si>
-    <t>***Call ins to get bar code letter if needed and insights on denials</t>
+    <t>Call ins to get bar code letter if needed and insights on denials</t>
   </si>
   <si>
     <t>22856 x1</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">Adjusted balance - no auth found - DND Acodes missing auth  </t>
   </si>
   <si>
-    <t>***DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</t>
+    <t>DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</t>
   </si>
   <si>
     <t xml:space="preserve">Adjusted balance - Acodes no covered with BCBS M2K - DND missing auth </t>
@@ -3698,7 +3698,7 @@
     <t>Uploaded MR - Barcode OC2007391060002 - Confirmation ID 1000086071082</t>
   </si>
   <si>
-    <t>*** DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</t>
+    <t> DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</t>
   </si>
   <si>
     <t>Uploaded MR - Barcode OC2007391060001 - Confirmation ID 1000086072612</t>

--- a/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-06 June - Specialty Claims.xlsx
@@ -2648,7 +2648,7 @@
     <t>HF552622415</t>
   </si>
   <si>
-    <t>76937+26 x1</t>
+    <t>75774+26+XU x4; 36245+59 x1; 36248+59 x2; 76937+26 x1; 75710+26+XU+RT x1; 37242 x1; 36246+59+RT x1</t>
   </si>
   <si>
     <t>26, 59</t>
@@ -3041,7 +3041,7 @@
     <t>HF556915332</t>
   </si>
   <si>
-    <t>63685 x1, 63650 x2</t>
+    <t>63685 x1</t>
   </si>
   <si>
     <t>210</t>
